--- a/files/NRL_futures_sim.xlsx
+++ b/files/NRL_futures_sim.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <si>
     <t xml:space="preserve">Team</t>
   </si>
@@ -35,10 +35,10 @@
     <t xml:space="preserve">New Zealand Warriors</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97</t>
+    <t xml:space="preserve">3.66</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08</t>
   </si>
   <si>
     <t xml:space="preserve">1.00</t>
@@ -50,7 +50,7 @@
     <t xml:space="preserve">Penrith Panthers</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82</t>
+    <t xml:space="preserve">3.77</t>
   </si>
   <si>
     <t xml:space="preserve">2.14</t>
@@ -59,55 +59,61 @@
     <t xml:space="preserve">Dolphins</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67</t>
+    <t xml:space="preserve">5.44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cronulla Sharks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85</t>
   </si>
   <si>
     <t xml:space="preserve">Sydney Roosters</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cronulla Sharks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66</t>
+    <t xml:space="preserve">11.26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18</t>
   </si>
   <si>
     <t xml:space="preserve">South Sydney Rabbitohs</t>
   </si>
   <si>
-    <t xml:space="preserve">19.55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54</t>
+    <t xml:space="preserve">21.95</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44</t>
   </si>
   <si>
     <t xml:space="preserve">Newcastle Knights</t>
   </si>
   <si>
-    <t xml:space="preserve">39.45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.23</t>
+    <t xml:space="preserve">33.90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.18</t>
   </si>
   <si>
     <t xml:space="preserve">NQ Cowboys</t>
   </si>
   <si>
-    <t xml:space="preserve">130.72</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.10</t>
+    <t xml:space="preserve">124.22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.65</t>
   </si>
   <si>
     <t xml:space="preserve">Brisbane Broncos</t>
@@ -562,7 +568,7 @@
         <v>19</v>
       </c>
       <c r="D5" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -573,16 +579,16 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -593,13 +599,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D7" t="s">
         <v>10</v>
@@ -613,13 +619,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D8" t="s">
         <v>10</v>
@@ -633,13 +639,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C9" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D9" t="s">
         <v>10</v>
@@ -653,7 +659,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B10" t="s">
         <v>10</v>
@@ -673,7 +679,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B11" t="s">
         <v>10</v>
@@ -693,7 +699,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B12" t="s">
         <v>10</v>
@@ -713,7 +719,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B13" t="s">
         <v>10</v>
@@ -733,7 +739,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B14" t="s">
         <v>10</v>
@@ -753,7 +759,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B15" t="s">
         <v>10</v>
@@ -773,7 +779,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B16" t="s">
         <v>10</v>
@@ -793,7 +799,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B17" t="s">
         <v>10</v>
@@ -813,7 +819,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B18" t="s">
         <v>10</v>

--- a/files/NRL_futures_sim.xlsx
+++ b/files/NRL_futures_sim.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t xml:space="preserve">Team</t>
   </si>
@@ -32,28 +32,28 @@
     <t xml:space="preserve">Miss Top 8 Odds</t>
   </si>
   <si>
+    <t xml:space="preserve">Penrith Panthers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-</t>
+  </si>
+  <si>
     <t xml:space="preserve">New Zealand Warriors</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Penrith Panthers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14</t>
+    <t xml:space="preserve">3.89</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12</t>
   </si>
   <si>
     <t xml:space="preserve">Dolphins</t>
@@ -62,58 +62,52 @@
     <t xml:space="preserve">5.44</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54</t>
+    <t xml:space="preserve">2.55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sydney Roosters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Sydney Rabbitohs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.84</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Newcastle Knights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.52</t>
   </si>
   <si>
     <t xml:space="preserve">Cronulla Sharks</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sydney Roosters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">South Sydney Rabbitohs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.95</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Newcastle Knights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.90</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.18</t>
+    <t xml:space="preserve">28.41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.16</t>
   </si>
   <si>
     <t xml:space="preserve">NQ Cowboys</t>
   </si>
   <si>
-    <t xml:space="preserve">124.22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.65</t>
+    <t xml:space="preserve">119.76</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.34</t>
   </si>
   <si>
     <t xml:space="preserve">Brisbane Broncos</t>
@@ -568,7 +562,7 @@
         <v>19</v>
       </c>
       <c r="D5" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -579,16 +573,16 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
         <v>21</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>22</v>
       </c>
-      <c r="C6" t="s">
-        <v>23</v>
-      </c>
       <c r="D6" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -599,13 +593,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
         <v>25</v>
-      </c>
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" t="s">
-        <v>27</v>
       </c>
       <c r="D7" t="s">
         <v>10</v>
@@ -619,13 +613,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s">
         <v>28</v>
-      </c>
-      <c r="B8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" t="s">
-        <v>30</v>
       </c>
       <c r="D8" t="s">
         <v>10</v>
@@ -639,13 +633,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" t="s">
         <v>31</v>
-      </c>
-      <c r="B9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" t="s">
-        <v>33</v>
       </c>
       <c r="D9" t="s">
         <v>10</v>
@@ -659,7 +653,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B10" t="s">
         <v>10</v>
@@ -679,7 +673,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B11" t="s">
         <v>10</v>
@@ -699,7 +693,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B12" t="s">
         <v>10</v>
@@ -719,7 +713,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B13" t="s">
         <v>10</v>
@@ -739,7 +733,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B14" t="s">
         <v>10</v>
@@ -759,7 +753,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B15" t="s">
         <v>10</v>
@@ -779,7 +773,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B16" t="s">
         <v>10</v>
@@ -799,7 +793,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B17" t="s">
         <v>10</v>
@@ -819,7 +813,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B18" t="s">
         <v>10</v>

--- a/files/NRL_futures_sim.xlsx
+++ b/files/NRL_futures_sim.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <si>
     <t xml:space="preserve">Team</t>
   </si>
@@ -35,10 +35,10 @@
     <t xml:space="preserve">Penrith Panthers</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11</t>
+    <t xml:space="preserve">3.72</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09</t>
   </si>
   <si>
     <t xml:space="preserve">1.00</t>
@@ -50,64 +50,70 @@
     <t xml:space="preserve">New Zealand Warriors</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12</t>
+    <t xml:space="preserve">3.92</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15</t>
   </si>
   <si>
     <t xml:space="preserve">Dolphins</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55</t>
+    <t xml:space="preserve">5.37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58</t>
   </si>
   <si>
     <t xml:space="preserve">Sydney Roosters</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74</t>
+    <t xml:space="preserve">6.39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Newcastle Knights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.44</t>
   </si>
   <si>
     <t xml:space="preserve">South Sydney Rabbitohs</t>
   </si>
   <si>
-    <t xml:space="preserve">24.84</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.67</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Newcastle Knights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.52</t>
+    <t xml:space="preserve">23.28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.58</t>
   </si>
   <si>
     <t xml:space="preserve">Cronulla Sharks</t>
   </si>
   <si>
-    <t xml:space="preserve">28.41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.16</t>
+    <t xml:space="preserve">28.25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.48</t>
   </si>
   <si>
     <t xml:space="preserve">NQ Cowboys</t>
   </si>
   <si>
-    <t xml:space="preserve">119.76</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.34</t>
+    <t xml:space="preserve">122.70</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.26</t>
   </si>
   <si>
     <t xml:space="preserve">Brisbane Broncos</t>
@@ -562,7 +568,7 @@
         <v>19</v>
       </c>
       <c r="D5" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -573,16 +579,16 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -593,13 +599,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D7" t="s">
         <v>10</v>
@@ -613,13 +619,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D8" t="s">
         <v>10</v>
@@ -633,13 +639,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C9" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D9" t="s">
         <v>10</v>
@@ -653,7 +659,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B10" t="s">
         <v>10</v>
@@ -673,7 +679,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B11" t="s">
         <v>10</v>
@@ -693,7 +699,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B12" t="s">
         <v>10</v>
@@ -713,7 +719,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B13" t="s">
         <v>10</v>
@@ -733,7 +739,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B14" t="s">
         <v>10</v>
@@ -753,7 +759,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B15" t="s">
         <v>10</v>
@@ -773,7 +779,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B16" t="s">
         <v>10</v>
@@ -793,7 +799,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B17" t="s">
         <v>10</v>
@@ -813,7 +819,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B18" t="s">
         <v>10</v>
